--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484149_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484149_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9565</v>
+        <v>2.5239</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6427</v>
+        <v>3.7051</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6862</v>
+        <v>-1.1812</v>
       </c>
       <c r="G2" t="n">
         <v>0.8539</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5248</v>
+        <v>0.0425</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4817</v>
+        <v>-0.4193</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0432</v>
+        <v>0.4618</v>
       </c>
       <c r="V2" t="n">
         <v>3.0162</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8024</v>
+        <v>1.0562</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3024</v>
+        <v>0.7526</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.3036</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6509</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.997</v>
+        <v>0.2508</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2495</v>
+        <v>-0.3003</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.5511</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BALTÀ CASTELLTORT</t>
+          <t>B. ENRICH TASIAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6444</v>
+        <v>0.74</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1415</v>
+        <v>0.4487</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5029</v>
+        <v>0.2914</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0507</v>
+        <v>-0.3077</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5829</v>
+        <v>0.8253</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9468</v>
+        <v>1.1061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.746</v>
+        <v>0.4234</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2008</v>
+        <v>0.6827</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5804</v>
+        <v>-0.5886</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7967</v>
+        <v>-0.7311</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7837</v>
+        <v>0.1425</v>
       </c>
       <c r="P4" t="n">
         <v>0.3968</v>
@@ -766,28 +766,28 @@
         <v>0.5952</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8813</v>
+        <v>-0.1743</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8728</v>
+        <v>-0.4591</v>
       </c>
       <c r="U4" t="n">
-        <v>1.7541</v>
+        <v>0.2848</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ENRICH TASIAS</t>
+          <t>A. BALTÀ CASTELLTORT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3232</v>
+        <v>0.1074</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2843</v>
+        <v>0.3059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0389</v>
+        <v>-0.1985</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5175999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3077</v>
+        <v>-0.0507</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8253</v>
+        <v>-0.5829</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1061</v>
+        <v>0.9468</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4234</v>
+        <v>0.746</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6827</v>
+        <v>0.2008</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5886</v>
+        <v>-1.5804</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7311</v>
+        <v>-0.7967</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1425</v>
+        <v>-0.7837</v>
       </c>
       <c r="P5" t="n">
         <v>0.3968</v>
@@ -844,22 +844,22 @@
         <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5911999999999999</v>
+        <v>0.3443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.7085</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0323</v>
+        <v>1.0528</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3093</v>
+        <v>-0.2212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6373</v>
+        <v>0.3313</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3281</v>
+        <v>-0.5525</v>
       </c>
       <c r="G6" t="n">
         <v>1.4306</v>
@@ -922,13 +922,13 @@
         <v>0.9919</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6722</v>
+        <v>0.1417</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2436</v>
+        <v>-0.5497</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.6914</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6032</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8277</v>
+        <v>-0.4017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4797</v>
+        <v>0.9898</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3074</v>
+        <v>-1.3915</v>
       </c>
       <c r="G7" t="n">
         <v>2.9313</v>
@@ -1000,13 +1000,13 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5606</v>
+        <v>-0.1346</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1619</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6012</v>
+        <v>0.5171</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8097</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>S. QUINTANA CALVENTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2644</v>
+        <v>-0.8273</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4183</v>
+        <v>0.0308</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8462</v>
+        <v>-0.8582</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6627</v>
+        <v>0.4476</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3736</v>
+        <v>0.9425</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2891</v>
+        <v>-0.4949</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6362</v>
+        <v>1.1478</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5259</v>
+        <v>1.2606</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1103</v>
+        <v>-0.1128</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0265</v>
+        <v>-0.7002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8476</v>
+        <v>-0.3181</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1788</v>
+        <v>-0.3821</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9838</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2601</v>
+        <v>-0.3344</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0115</v>
+        <v>-0.391</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2716</v>
+        <v>0.0566</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6745</v>
+        <v>-0.9405</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. QUINTANA CALVENTE</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3477</v>
+        <v>-1.1956</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3773</v>
+        <v>-0.8264</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9704</v>
+        <v>-0.3692</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4476</v>
+        <v>-3.6627</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9425</v>
+        <v>-2.3736</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4949</v>
+        <v>-1.2891</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1478</v>
+        <v>-1.6362</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2606</v>
+        <v>-1.5259</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1128</v>
+        <v>-0.1103</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7002</v>
+        <v>-2.0265</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3181</v>
+        <v>-0.8476</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3821</v>
+        <v>-1.1788</v>
       </c>
       <c r="P9" t="n">
+        <v>1.9838</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-0.9919</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8548</v>
+        <v>-0.1913</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7991</v>
+        <v>-0.3966</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0556</v>
+        <v>0.2053</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>0.6745</v>
       </c>
       <c r="W9" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0321</v>
+        <v>-2.906</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1784</v>
+        <v>-2.912</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1463</v>
+        <v>0.006</v>
       </c>
       <c r="G10" t="n">
         <v>-4.2337</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1276</v>
+        <v>-0.0014</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9238</v>
+        <v>-0.6574</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7963</v>
+        <v>0.656</v>
       </c>
       <c r="V10" t="n">
         <v>0.3373</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4361</v>
+        <v>-1.1243</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5139</v>
+        <v>2.8258</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9502</v>
+        <v>-3.9501</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9999</v>
@@ -1312,13 +1312,13 @@
         <v>10.9112</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3685999999999999</v>
+        <v>-0.05669999999999996</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.845400000000001</v>
+        <v>-4.5336</v>
       </c>
       <c r="U11" t="n">
-        <v>4.4768</v>
+        <v>4.4769</v>
       </c>
       <c r="V11" t="n">
         <v>0.9405999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1355</v>
+        <v>3.5327</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5833</v>
+        <v>3.2975</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5523</v>
+        <v>0.2352</v>
       </c>
       <c r="G12" t="n">
         <v>2.3819</v>
@@ -1390,13 +1390,13 @@
         <v>1.1903</v>
       </c>
       <c r="S12" t="n">
-        <v>0.412</v>
+        <v>0.8091</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0485</v>
+        <v>-0.3343</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4605</v>
+        <v>1.1434</v>
       </c>
       <c r="V12" t="n">
         <v>1.1352</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. ACOSTA ALMONTE</t>
+          <t>G. FABREGAS CANALS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6309</v>
+        <v>2.5455</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0034</v>
+        <v>1.519</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6274999999999999</v>
+        <v>1.0265</v>
       </c>
       <c r="G13" t="n">
-        <v>1.584</v>
+        <v>1.7982</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8496</v>
+        <v>-0.3731</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2656</v>
+        <v>2.1713</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5726</v>
+        <v>2.7558</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5726</v>
+        <v>0.3385</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4174</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0114</v>
+        <v>-0.9576</v>
       </c>
       <c r="N13" t="n">
-        <v>0.277</v>
+        <v>-0.7116</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2656</v>
+        <v>-0.2461</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4518</v>
+        <v>-0.0028</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4308</v>
+        <v>-0.7254</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0209</v>
+        <v>0.7226</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5437</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.0713</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. FABREGAS CANALS</t>
+          <t>D. ACOSTA ALMONTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8432</v>
+        <v>2.3308</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0089</v>
+        <v>1.5953</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8343</v>
+        <v>0.7355</v>
       </c>
       <c r="G14" t="n">
-        <v>1.7982</v>
+        <v>1.584</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3731</v>
+        <v>1.8496</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1713</v>
+        <v>-0.2656</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7558</v>
+        <v>1.5726</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3385</v>
+        <v>1.5726</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4174</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9576</v>
+        <v>0.0114</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7116</v>
+        <v>0.277</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2461</v>
+        <v>-0.2656</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1903</v>
+        <v>0.5952</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.1516</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2356</v>
+        <v>0.0227</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5304</v>
+        <v>0.1289</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5437</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0713</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7245</v>
+        <v>0.9805</v>
       </c>
       <c r="E15" t="n">
-        <v>1.498</v>
+        <v>0.4777</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2265</v>
+        <v>0.5028</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2954</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1308</v>
+        <v>0.3869</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5443</v>
+        <v>-0.476</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5865</v>
+        <v>0.8628</v>
       </c>
       <c r="V15" t="n">
         <v>1.881</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>P. MAJORAL DE LOS RIOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1756</v>
+        <v>0.979</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5755</v>
+        <v>0.3742</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4</v>
+        <v>0.6048</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.277</v>
+        <v>0.8703</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8566</v>
+        <v>-0.2322</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1336</v>
+        <v>1.1025</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4937</v>
+        <v>1.9786</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9731</v>
+        <v>0.0859</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4794</v>
+        <v>1.8927</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-1.1083</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1165</v>
+        <v>-0.3181</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6542</v>
+        <v>-0.7902</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3887</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.9919</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.1903</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.3556</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.8784999999999999</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.5228</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3887</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.0044</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.5499000000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.4545</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-0.9405</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-1.4724</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MAJORAL DE LOS RIOS</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2844</v>
+        <v>0.4291</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.8613</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2162</v>
+        <v>-0.4322</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8703</v>
+        <v>-0.277</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2322</v>
+        <v>0.8566</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1025</v>
+        <v>-1.1336</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9786</v>
+        <v>0.4937</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0859</v>
+        <v>0.9731</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8927</v>
+        <v>-0.4794</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1083</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3181</v>
+        <v>-0.1165</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7902</v>
+        <v>-0.6542</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>1.3887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0503</v>
+        <v>0.2579</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1846</v>
+        <v>-0.1643</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1343</v>
+        <v>0.4222</v>
       </c>
       <c r="V17" t="n">
-        <v>0.266</v>
+        <v>-0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0.532</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0002</v>
+        <v>-0.6702</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0574</v>
+        <v>0.2487</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9428</v>
+        <v>-0.9189000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>0.2188</v>
@@ -1858,13 +1858,13 @@
         <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4092</v>
+        <v>-0.0793</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9238</v>
+        <v>-0.6177</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5384</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5174</v>
+        <v>-1.173</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4422</v>
+        <v>-1.2381</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0752</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>0.0405</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4903</v>
+        <v>-0.146</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8615</v>
+        <v>-0.6574</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3712</v>
+        <v>0.5115</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8692</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2528</v>
+        <v>-2.819</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4203</v>
+        <v>-1.9305</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8324</v>
+        <v>-0.8885</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1628</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>1.323</v>
+        <v>0.7567</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5613</v>
+        <v>0.0511</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7617</v>
+        <v>0.7056</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5878</v>
+        <v>-3.3388</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8672</v>
+        <v>-1.255</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7206</v>
+        <v>-2.0838</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1585</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2985</v>
+        <v>-0.0496</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3092</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0107</v>
+        <v>0.6475</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5437</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.435899999999998</v>
+        <v>2.796600000000002</v>
       </c>
       <c r="E22" t="n">
         <v>3.9501</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.514200000000001</v>
+        <v>-1.1535</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -2161,7 +2161,7 @@
         <v>-5.2141</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9918000000000003</v>
+        <v>-0.9918000000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-10.911</v>
@@ -2170,19 +2170,19 @@
         <v>9.9192</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3685999999999998</v>
+        <v>1.7289</v>
       </c>
       <c r="T22" t="n">
         <v>-4.4769</v>
       </c>
       <c r="U22" t="n">
-        <v>4.8453</v>
+        <v>6.205700000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9405000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>6.279299999999999</v>
+        <v>6.2793</v>
       </c>
       <c r="X22" t="n">
         <v>-7.2197</v>
